--- a/data/live/scanner_output_latest.xlsx
+++ b/data/live/scanner_output_latest.xlsx
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="CH2" t="n">
-        <v>252.08</v>
+        <v>262.02</v>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
@@ -2235,7 +2235,7 @@
         </is>
       </c>
       <c r="CJ2" t="n">
-        <v>252.08</v>
+        <v>262.02</v>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:05-04:00</t>
+          <t>2026-08-01 00:22:01-04:00</t>
         </is>
       </c>
       <c r="CM2" t="b">
@@ -3001,7 +3001,7 @@
         </is>
       </c>
       <c r="CH3" t="n">
-        <v>252.1</v>
+        <v>262.03</v>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
@@ -3009,7 +3009,7 @@
         </is>
       </c>
       <c r="CJ3" t="n">
-        <v>252.1</v>
+        <v>262.03</v>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
@@ -3018,7 +3018,7 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:05-04:00</t>
+          <t>2026-08-01 00:22:02-04:00</t>
         </is>
       </c>
       <c r="CM3" t="b">
@@ -3769,7 +3769,7 @@
         </is>
       </c>
       <c r="CH4" t="n">
-        <v>252.1</v>
+        <v>262.04</v>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="CJ4" t="n">
-        <v>252.1</v>
+        <v>262.04</v>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
@@ -3786,7 +3786,7 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:06-04:00</t>
+          <t>2026-08-01 00:22:02-04:00</t>
         </is>
       </c>
       <c r="CM4" t="b">
@@ -4529,7 +4529,7 @@
         </is>
       </c>
       <c r="CH5" t="n">
-        <v>252.11</v>
+        <v>262.05</v>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="CJ5" t="n">
-        <v>252.11</v>
+        <v>262.05</v>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:06-04:00</t>
+          <t>2026-08-01 00:22:03-04:00</t>
         </is>
       </c>
       <c r="CM5" t="b">
@@ -5299,7 +5299,7 @@
         </is>
       </c>
       <c r="CH6" t="n">
-        <v>252.12</v>
+        <v>262.07</v>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
@@ -5307,7 +5307,7 @@
         </is>
       </c>
       <c r="CJ6" t="n">
-        <v>252.12</v>
+        <v>262.07</v>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
@@ -5316,7 +5316,7 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:07-04:00</t>
+          <t>2026-08-01 00:22:04-04:00</t>
         </is>
       </c>
       <c r="CM6" t="b">
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="CH7" t="n">
-        <v>252.13</v>
+        <v>262.08</v>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
@@ -6079,7 +6079,7 @@
         </is>
       </c>
       <c r="CJ7" t="n">
-        <v>252.13</v>
+        <v>262.08</v>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
@@ -6088,7 +6088,7 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:07-04:00</t>
+          <t>2026-08-01 00:22:04-04:00</t>
         </is>
       </c>
       <c r="CM7" t="b">
@@ -6841,7 +6841,7 @@
         </is>
       </c>
       <c r="CH8" t="n">
-        <v>252.18</v>
+        <v>262.09</v>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         </is>
       </c>
       <c r="CJ8" t="n">
-        <v>252.18</v>
+        <v>262.09</v>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
@@ -6858,7 +6858,7 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:10-04:00</t>
+          <t>2026-08-01 00:22:05-04:00</t>
         </is>
       </c>
       <c r="CM8" t="b">
@@ -7599,7 +7599,7 @@
         </is>
       </c>
       <c r="CH9" t="n">
-        <v>252.19</v>
+        <v>262.1</v>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
@@ -7607,7 +7607,7 @@
         </is>
       </c>
       <c r="CJ9" t="n">
-        <v>252.19</v>
+        <v>262.1</v>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
@@ -7616,7 +7616,7 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:11-04:00</t>
+          <t>2026-08-01 00:22:06-04:00</t>
         </is>
       </c>
       <c r="CM9" t="b">
@@ -8363,7 +8363,7 @@
         </is>
       </c>
       <c r="CH10" t="n">
-        <v>252.19</v>
+        <v>262.11</v>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="CJ10" t="n">
-        <v>252.19</v>
+        <v>262.11</v>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
@@ -8380,7 +8380,7 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:11-04:00</t>
+          <t>2026-08-01 00:22:06-04:00</t>
         </is>
       </c>
       <c r="CM10" t="b">
@@ -9133,7 +9133,7 @@
         </is>
       </c>
       <c r="CH11" t="n">
-        <v>252.2</v>
+        <v>262.12</v>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
@@ -9141,7 +9141,7 @@
         </is>
       </c>
       <c r="CJ11" t="n">
-        <v>252.2</v>
+        <v>262.12</v>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:12-04:00</t>
+          <t>2026-08-01 00:22:07-04:00</t>
         </is>
       </c>
       <c r="CM11" t="b">
@@ -9897,7 +9897,7 @@
         </is>
       </c>
       <c r="CH12" t="n">
-        <v>252.21</v>
+        <v>262.13</v>
       </c>
       <c r="CI12" t="inlineStr">
         <is>
@@ -9905,7 +9905,7 @@
         </is>
       </c>
       <c r="CJ12" t="n">
-        <v>252.21</v>
+        <v>262.13</v>
       </c>
       <c r="CK12" t="inlineStr">
         <is>
@@ -9914,7 +9914,7 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:12-04:00</t>
+          <t>2026-08-01 00:22:08-04:00</t>
         </is>
       </c>
       <c r="CM12" t="b">
@@ -10677,7 +10677,7 @@
         </is>
       </c>
       <c r="CH13" t="n">
-        <v>252.22</v>
+        <v>262.15</v>
       </c>
       <c r="CI13" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         </is>
       </c>
       <c r="CJ13" t="n">
-        <v>252.22</v>
+        <v>262.15</v>
       </c>
       <c r="CK13" t="inlineStr">
         <is>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="CL13" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:13-04:00</t>
+          <t>2026-08-01 00:22:08-04:00</t>
         </is>
       </c>
       <c r="CM13" t="b">
@@ -11455,7 +11455,7 @@
         </is>
       </c>
       <c r="CH14" t="n">
-        <v>252.22</v>
+        <v>262.16</v>
       </c>
       <c r="CI14" t="inlineStr">
         <is>
@@ -11463,7 +11463,7 @@
         </is>
       </c>
       <c r="CJ14" t="n">
-        <v>252.22</v>
+        <v>262.16</v>
       </c>
       <c r="CK14" t="inlineStr">
         <is>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="CL14" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:13-04:00</t>
+          <t>2026-08-01 00:22:09-04:00</t>
         </is>
       </c>
       <c r="CM14" t="b">
@@ -12233,7 +12233,7 @@
         </is>
       </c>
       <c r="CH15" t="n">
-        <v>252.23</v>
+        <v>262.17</v>
       </c>
       <c r="CI15" t="inlineStr">
         <is>
@@ -12241,7 +12241,7 @@
         </is>
       </c>
       <c r="CJ15" t="n">
-        <v>252.23</v>
+        <v>262.17</v>
       </c>
       <c r="CK15" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
       </c>
       <c r="CL15" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:14-04:00</t>
+          <t>2026-08-01 00:22:10-04:00</t>
         </is>
       </c>
       <c r="CM15" t="b">
@@ -13005,7 +13005,7 @@
         </is>
       </c>
       <c r="CH16" t="n">
-        <v>252.24</v>
+        <v>262.18</v>
       </c>
       <c r="CI16" t="inlineStr">
         <is>
@@ -13013,7 +13013,7 @@
         </is>
       </c>
       <c r="CJ16" t="n">
-        <v>252.24</v>
+        <v>262.18</v>
       </c>
       <c r="CK16" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
       </c>
       <c r="CL16" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:14-04:00</t>
+          <t>2026-08-01 00:22:10-04:00</t>
         </is>
       </c>
       <c r="CM16" t="b">
@@ -13761,7 +13761,7 @@
         </is>
       </c>
       <c r="CH17" t="n">
-        <v>252.25</v>
+        <v>262.19</v>
       </c>
       <c r="CI17" t="inlineStr">
         <is>
@@ -13769,7 +13769,7 @@
         </is>
       </c>
       <c r="CJ17" t="n">
-        <v>252.25</v>
+        <v>262.19</v>
       </c>
       <c r="CK17" t="inlineStr">
         <is>
@@ -13778,7 +13778,7 @@
       </c>
       <c r="CL17" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:14-04:00</t>
+          <t>2026-08-01 00:22:11-04:00</t>
         </is>
       </c>
       <c r="CM17" t="b">
@@ -14521,7 +14521,7 @@
         </is>
       </c>
       <c r="CH18" t="n">
-        <v>252.26</v>
+        <v>262.2</v>
       </c>
       <c r="CI18" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         </is>
       </c>
       <c r="CJ18" t="n">
-        <v>252.26</v>
+        <v>262.2</v>
       </c>
       <c r="CK18" t="inlineStr">
         <is>
@@ -14538,7 +14538,7 @@
       </c>
       <c r="CL18" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:15-04:00</t>
+          <t>2026-08-01 00:22:12-04:00</t>
         </is>
       </c>
       <c r="CM18" t="b">
@@ -15299,7 +15299,7 @@
         </is>
       </c>
       <c r="CH19" t="n">
-        <v>252.26</v>
+        <v>262.21</v>
       </c>
       <c r="CI19" t="inlineStr">
         <is>
@@ -15307,7 +15307,7 @@
         </is>
       </c>
       <c r="CJ19" t="n">
-        <v>252.26</v>
+        <v>262.21</v>
       </c>
       <c r="CK19" t="inlineStr">
         <is>
@@ -15316,7 +15316,7 @@
       </c>
       <c r="CL19" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:15-04:00</t>
+          <t>2026-08-01 00:22:12-04:00</t>
         </is>
       </c>
       <c r="CM19" t="b">
@@ -16077,7 +16077,7 @@
         </is>
       </c>
       <c r="CH20" t="n">
-        <v>252.27</v>
+        <v>262.23</v>
       </c>
       <c r="CI20" t="inlineStr">
         <is>
@@ -16085,7 +16085,7 @@
         </is>
       </c>
       <c r="CJ20" t="n">
-        <v>252.27</v>
+        <v>262.23</v>
       </c>
       <c r="CK20" t="inlineStr">
         <is>
@@ -16094,7 +16094,7 @@
       </c>
       <c r="CL20" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:16-04:00</t>
+          <t>2026-08-01 00:22:13-04:00</t>
         </is>
       </c>
       <c r="CM20" t="b">
@@ -16849,7 +16849,7 @@
         </is>
       </c>
       <c r="CH21" t="n">
-        <v>252.28</v>
+        <v>262.24</v>
       </c>
       <c r="CI21" t="inlineStr">
         <is>
@@ -16857,7 +16857,7 @@
         </is>
       </c>
       <c r="CJ21" t="n">
-        <v>252.28</v>
+        <v>262.24</v>
       </c>
       <c r="CK21" t="inlineStr">
         <is>
@@ -16866,7 +16866,7 @@
       </c>
       <c r="CL21" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:16-04:00</t>
+          <t>2026-08-01 00:22:14-04:00</t>
         </is>
       </c>
       <c r="CM21" t="b">
@@ -17619,7 +17619,7 @@
         </is>
       </c>
       <c r="CH22" t="n">
-        <v>252.29</v>
+        <v>262.26</v>
       </c>
       <c r="CI22" t="inlineStr">
         <is>
@@ -17627,7 +17627,7 @@
         </is>
       </c>
       <c r="CJ22" t="n">
-        <v>252.29</v>
+        <v>262.26</v>
       </c>
       <c r="CK22" t="inlineStr">
         <is>
@@ -17636,7 +17636,7 @@
       </c>
       <c r="CL22" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:17-04:00</t>
+          <t>2026-08-01 00:22:15-04:00</t>
         </is>
       </c>
       <c r="CM22" t="b">
@@ -18389,7 +18389,7 @@
         </is>
       </c>
       <c r="CH23" t="n">
-        <v>252.29</v>
+        <v>262.27</v>
       </c>
       <c r="CI23" t="inlineStr">
         <is>
@@ -18397,7 +18397,7 @@
         </is>
       </c>
       <c r="CJ23" t="n">
-        <v>252.29</v>
+        <v>262.27</v>
       </c>
       <c r="CK23" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
       </c>
       <c r="CL23" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:17-04:00</t>
+          <t>2026-08-01 00:22:16-04:00</t>
         </is>
       </c>
       <c r="CM23" t="b">
@@ -19163,7 +19163,7 @@
         </is>
       </c>
       <c r="CH24" t="n">
-        <v>252.3</v>
+        <v>262.28</v>
       </c>
       <c r="CI24" t="inlineStr">
         <is>
@@ -19171,7 +19171,7 @@
         </is>
       </c>
       <c r="CJ24" t="n">
-        <v>252.3</v>
+        <v>262.28</v>
       </c>
       <c r="CK24" t="inlineStr">
         <is>
@@ -19180,7 +19180,7 @@
       </c>
       <c r="CL24" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:18-04:00</t>
+          <t>2026-08-01 00:22:16-04:00</t>
         </is>
       </c>
       <c r="CM24" t="b">
@@ -19939,7 +19939,7 @@
         </is>
       </c>
       <c r="CH25" t="n">
-        <v>252.31</v>
+        <v>262.43</v>
       </c>
       <c r="CI25" t="inlineStr">
         <is>
@@ -19947,7 +19947,7 @@
         </is>
       </c>
       <c r="CJ25" t="n">
-        <v>252.31</v>
+        <v>262.43</v>
       </c>
       <c r="CK25" t="inlineStr">
         <is>
@@ -19956,7 +19956,7 @@
       </c>
       <c r="CL25" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:18-04:00</t>
+          <t>2026-08-01 00:22:26-04:00</t>
         </is>
       </c>
       <c r="CM25" t="b">
@@ -20707,7 +20707,7 @@
         </is>
       </c>
       <c r="CH26" t="n">
-        <v>297.32</v>
+        <v>307.45</v>
       </c>
       <c r="CI26" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
         </is>
       </c>
       <c r="CJ26" t="n">
-        <v>297.32</v>
+        <v>307.45</v>
       </c>
       <c r="CK26" t="inlineStr">
         <is>
@@ -20724,7 +20724,7 @@
       </c>
       <c r="CL26" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:19-04:00</t>
+          <t>2026-08-01 00:22:26-04:00</t>
         </is>
       </c>
       <c r="CM26" t="b">
@@ -21479,7 +21479,7 @@
         </is>
       </c>
       <c r="CH27" t="n">
-        <v>252.32</v>
+        <v>262.46</v>
       </c>
       <c r="CI27" t="inlineStr">
         <is>
@@ -21487,7 +21487,7 @@
         </is>
       </c>
       <c r="CJ27" t="n">
-        <v>252.32</v>
+        <v>262.46</v>
       </c>
       <c r="CK27" t="inlineStr">
         <is>
@@ -21496,7 +21496,7 @@
       </c>
       <c r="CL27" t="inlineStr">
         <is>
-          <t>2026-08-01 00:12:19-04:00</t>
+          <t>2026-08-01 00:22:27-04:00</t>
         </is>
       </c>
       <c r="CM27" t="b">

--- a/data/live/scanner_output_latest.xlsx
+++ b/data/live/scanner_output_latest.xlsx
@@ -1228,7 +1228,7 @@
       <c r="BO2" t="inlineStr"/>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ2" t="b">
@@ -1556,7 +1556,7 @@
       <c r="BO3" t="inlineStr"/>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ3" t="b">
@@ -1884,7 +1884,7 @@
       <c r="BO4" t="inlineStr"/>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ4" t="b">
@@ -2212,7 +2212,7 @@
       <c r="BO5" t="inlineStr"/>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ5" t="b">
@@ -2540,7 +2540,7 @@
       <c r="BO6" t="inlineStr"/>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ6" t="b">
@@ -2868,7 +2868,7 @@
       <c r="BO7" t="inlineStr"/>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ7" t="b">
@@ -3196,7 +3196,7 @@
       <c r="BO8" t="inlineStr"/>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ8" t="b">
@@ -3524,7 +3524,7 @@
       <c r="BO9" t="inlineStr"/>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ9" t="b">
@@ -3852,7 +3852,7 @@
       <c r="BO10" t="inlineStr"/>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ10" t="b">
@@ -4180,7 +4180,7 @@
       <c r="BO11" t="inlineStr"/>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ11" t="b">
@@ -4508,7 +4508,7 @@
       <c r="BO12" t="inlineStr"/>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ12" t="b">
@@ -4836,7 +4836,7 @@
       <c r="BO13" t="inlineStr"/>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ13" t="b">
@@ -5164,7 +5164,7 @@
       <c r="BO14" t="inlineStr"/>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ14" t="b">
@@ -5492,7 +5492,7 @@
       <c r="BO15" t="inlineStr"/>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ15" t="b">
@@ -5820,7 +5820,7 @@
       <c r="BO16" t="inlineStr"/>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ16" t="b">
@@ -6148,7 +6148,7 @@
       <c r="BO17" t="inlineStr"/>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ17" t="b">
@@ -6476,7 +6476,7 @@
       <c r="BO18" t="inlineStr"/>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ18" t="b">
@@ -6804,7 +6804,7 @@
       <c r="BO19" t="inlineStr"/>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ19" t="b">
@@ -7132,7 +7132,7 @@
       <c r="BO20" t="inlineStr"/>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ20" t="b">
@@ -7460,7 +7460,7 @@
       <c r="BO21" t="inlineStr"/>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ21" t="b">
@@ -7788,7 +7788,7 @@
       <c r="BO22" t="inlineStr"/>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ22" t="b">
@@ -8116,7 +8116,7 @@
       <c r="BO23" t="inlineStr"/>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ23" t="b">
@@ -8444,7 +8444,7 @@
       <c r="BO24" t="inlineStr"/>
       <c r="BP24" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ24" t="b">
@@ -8772,7 +8772,7 @@
       <c r="BO25" t="inlineStr"/>
       <c r="BP25" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ25" t="b">
@@ -9100,7 +9100,7 @@
       <c r="BO26" t="inlineStr"/>
       <c r="BP26" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ26" t="b">
@@ -9428,7 +9428,7 @@
       <c r="BO27" t="inlineStr"/>
       <c r="BP27" t="inlineStr">
         <is>
-          <t>2026-08-01 09:46:37-04:00</t>
+          <t>2026-08-01 10:27:31-04:00</t>
         </is>
       </c>
       <c r="BQ27" t="b">
